--- a/NFL Project 2025.xlsx
+++ b/NFL Project 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5a94effdcb5c500/Desktop/Nfl Schedule Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{7B9D0AD1-81DC-4A1C-97F3-655F6E46017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B89BFD52-AC9D-4AF3-8675-29AE7E913EB2}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{7B9D0AD1-81DC-4A1C-97F3-655F6E46017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22298666-A567-4C8A-A1F8-AA0F3E1C8E5A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{3DCD2D9F-8671-4F82-ABFA-DA5D25767943}"/>
   </bookViews>
@@ -1235,7 +1235,7 @@
     <t>Nickname</t>
   </si>
   <si>
-    <t>Brian Thomas Jr</t>
+    <t>Brian Thomas</t>
   </si>
 </sst>
 </file>
@@ -1800,6 +1800,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/NFL Project 2025.xlsx
+++ b/NFL Project 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5a94effdcb5c500/Desktop/Nfl Schedule Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{7B9D0AD1-81DC-4A1C-97F3-655F6E46017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74F124B7-9D21-472F-9611-6BD3E09394F0}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{7B9D0AD1-81DC-4A1C-97F3-655F6E46017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C492571D-A004-4151-9207-E5200B59C933}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{3DCD2D9F-8671-4F82-ABFA-DA5D25767943}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" activeTab="1" xr2:uid="{3DCD2D9F-8671-4F82-ABFA-DA5D25767943}"/>
   </bookViews>
   <sheets>
     <sheet name="Defense DK Points" sheetId="1" r:id="rId1"/>
@@ -3071,6 +3071,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D02E207-BF85-429C-A761-3594BAE7010D}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
